--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.89473</v>
+        <v>16.9259</v>
       </c>
       <c r="D2" t="n">
-        <v>16.30387</v>
+        <v>16.44941</v>
       </c>
       <c r="E2" t="n">
-        <v>16.00911</v>
+        <v>16.62238</v>
       </c>
       <c r="F2" t="n">
-        <v>42.00245</v>
+        <v>42.64302</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04944</v>
+        <v>0.04989</v>
       </c>
       <c r="H2" t="n">
-        <v>1.78624</v>
+        <v>1.81057</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.8148</v>
+        <v>16.85251</v>
       </c>
       <c r="D3" t="n">
-        <v>16.49546</v>
+        <v>16.5545</v>
       </c>
       <c r="E3" t="n">
-        <v>16.94003</v>
+        <v>16.60829</v>
       </c>
       <c r="F3" t="n">
-        <v>42.44214</v>
+        <v>42.97084</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05031</v>
+        <v>0.05009</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82269</v>
+        <v>1.78986</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.67159</v>
+        <v>16.5844</v>
       </c>
       <c r="D4" t="n">
-        <v>16.22929</v>
+        <v>16.22509</v>
       </c>
       <c r="E4" t="n">
-        <v>16.80353</v>
+        <v>16.3219</v>
       </c>
       <c r="F4" t="n">
-        <v>42.95769</v>
+        <v>42.31465</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0513</v>
+        <v>0.04951</v>
       </c>
       <c r="H4" t="n">
-        <v>1.785</v>
+        <v>1.81288</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.56303</v>
+        <v>16.42422</v>
       </c>
       <c r="D6" t="n">
-        <v>15.788</v>
+        <v>16.02376</v>
       </c>
       <c r="E6" t="n">
-        <v>16.73873</v>
+        <v>16.12376</v>
       </c>
       <c r="F6" t="n">
-        <v>21.72832</v>
+        <v>21.6549</v>
       </c>
       <c r="G6" t="n">
-        <v>33.48262</v>
+        <v>33.62168</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.38244</v>
+        <v>16.3411</v>
       </c>
       <c r="D7" t="n">
-        <v>16.09301</v>
+        <v>15.90754</v>
       </c>
       <c r="E7" t="n">
-        <v>16.22115</v>
+        <v>16.27002</v>
       </c>
       <c r="F7" t="n">
-        <v>21.98112</v>
+        <v>20.75442</v>
       </c>
       <c r="G7" t="n">
-        <v>33.75635</v>
+        <v>34.40253</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.53684</v>
+        <v>16.70371</v>
       </c>
       <c r="D8" t="n">
-        <v>16.15023</v>
+        <v>15.88623</v>
       </c>
       <c r="E8" t="n">
-        <v>16.41319</v>
+        <v>16.51645</v>
       </c>
       <c r="F8" t="n">
-        <v>21.53627</v>
+        <v>21.92528</v>
       </c>
       <c r="G8" t="n">
-        <v>34.20534</v>
+        <v>34.31101</v>
       </c>
     </row>
   </sheetData>
